--- a/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
+++ b/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/03_MAKER/MK_PROJECTS/CMM_sobremMoradasDR/Brechamayo2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/CMMBML_Sobremesas_Modradas/BrechaPensiones21mayo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB60EA95-D2FC-4BB0-B434-386303B2B7E7}"/>
@@ -1116,6 +1116,111 @@
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="5" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="6" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="6" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="7" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="7" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="18" fillId="2" borderId="26" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1128,111 +1233,6 @@
     <xf numFmtId="15" fontId="3" fillId="2" borderId="0" xfId="9" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="6" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="6" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="7" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="7" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="5" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -1584,147 +1584,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="126"/>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="126"/>
-      <c r="S1" s="126"/>
-      <c r="T1" s="126"/>
-      <c r="U1" s="126"/>
-      <c r="V1" s="126"/>
-      <c r="W1" s="126"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="145"/>
+      <c r="O1" s="145"/>
+      <c r="P1" s="145"/>
+      <c r="Q1" s="145"/>
+      <c r="R1" s="145"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="145"/>
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
     </row>
     <row r="2" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="127" t="s">
+      <c r="A2" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="127"/>
-      <c r="Q2" s="127"/>
-      <c r="R2" s="126"/>
-      <c r="S2" s="126"/>
-      <c r="T2" s="126"/>
-      <c r="U2" s="126"/>
-      <c r="V2" s="126"/>
-      <c r="W2" s="126"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="146"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="146"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="145"/>
+      <c r="T2" s="145"/>
+      <c r="U2" s="145"/>
+      <c r="V2" s="145"/>
+      <c r="W2" s="145"/>
     </row>
     <row r="3" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="128" t="s">
+      <c r="A3" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="131" t="s">
+      <c r="B3" s="147" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="132"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="132"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="134" t="s">
+      <c r="C3" s="148"/>
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="135"/>
-      <c r="O3" s="135"/>
-      <c r="P3" s="135"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="137" t="s">
+      <c r="K3" s="151"/>
+      <c r="L3" s="151"/>
+      <c r="M3" s="151"/>
+      <c r="N3" s="151"/>
+      <c r="O3" s="151"/>
+      <c r="P3" s="151"/>
+      <c r="Q3" s="152"/>
+      <c r="R3" s="153" t="s">
         <v>5</v>
       </c>
-      <c r="S3" s="137"/>
-      <c r="T3" s="137"/>
-      <c r="U3" s="137"/>
-      <c r="V3" s="137"/>
-      <c r="W3" s="137"/>
-      <c r="X3" s="137"/>
-      <c r="Y3" s="137"/>
+      <c r="S3" s="153"/>
+      <c r="T3" s="153"/>
+      <c r="U3" s="153"/>
+      <c r="V3" s="153"/>
+      <c r="W3" s="153"/>
+      <c r="X3" s="153"/>
+      <c r="Y3" s="153"/>
     </row>
     <row r="4" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="129"/>
-      <c r="B4" s="138" t="s">
+      <c r="A4" s="137"/>
+      <c r="B4" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="139"/>
-      <c r="D4" s="138" t="s">
+      <c r="C4" s="129"/>
+      <c r="D4" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="140"/>
-      <c r="F4" s="141" t="s">
+      <c r="E4" s="130"/>
+      <c r="F4" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="142"/>
-      <c r="H4" s="143" t="s">
+      <c r="G4" s="154"/>
+      <c r="H4" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="143"/>
-      <c r="J4" s="138" t="s">
+      <c r="I4" s="125"/>
+      <c r="J4" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="139"/>
-      <c r="L4" s="138" t="s">
+      <c r="K4" s="129"/>
+      <c r="L4" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="140"/>
-      <c r="N4" s="141" t="s">
+      <c r="M4" s="130"/>
+      <c r="N4" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="153"/>
-      <c r="P4" s="146" t="s">
+      <c r="O4" s="132"/>
+      <c r="P4" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="146"/>
-      <c r="R4" s="154" t="s">
+      <c r="Q4" s="133"/>
+      <c r="R4" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="S4" s="155"/>
-      <c r="T4" s="154" t="s">
+      <c r="S4" s="123"/>
+      <c r="T4" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="U4" s="156"/>
-      <c r="V4" s="144" t="s">
+      <c r="U4" s="124"/>
+      <c r="V4" s="155" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="145"/>
-      <c r="X4" s="146" t="s">
+      <c r="W4" s="156"/>
+      <c r="X4" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" s="146"/>
+      <c r="Y4" s="133"/>
     </row>
     <row r="5" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="130"/>
+      <c r="A5" s="138"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3329,93 +3329,93 @@
       <c r="AH26" s="38"/>
     </row>
     <row r="27" spans="1:34" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="128" t="s">
+      <c r="A27" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="147" t="s">
+      <c r="B27" s="139" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="148"/>
-      <c r="D27" s="148"/>
-      <c r="E27" s="148"/>
-      <c r="F27" s="148"/>
-      <c r="G27" s="148"/>
-      <c r="H27" s="148"/>
-      <c r="I27" s="149"/>
-      <c r="J27" s="150" t="s">
+      <c r="C27" s="140"/>
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="140"/>
+      <c r="I27" s="141"/>
+      <c r="J27" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="K27" s="151"/>
-      <c r="L27" s="151"/>
-      <c r="M27" s="151"/>
-      <c r="N27" s="151"/>
-      <c r="O27" s="151"/>
-      <c r="P27" s="151"/>
-      <c r="Q27" s="151"/>
-      <c r="R27" s="152" t="s">
+      <c r="K27" s="143"/>
+      <c r="L27" s="143"/>
+      <c r="M27" s="143"/>
+      <c r="N27" s="143"/>
+      <c r="O27" s="143"/>
+      <c r="P27" s="143"/>
+      <c r="Q27" s="143"/>
+      <c r="R27" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="S27" s="152"/>
-      <c r="T27" s="152"/>
-      <c r="U27" s="152"/>
-      <c r="V27" s="152"/>
-      <c r="W27" s="152"/>
-      <c r="X27" s="152"/>
-      <c r="Y27" s="152"/>
+      <c r="S27" s="144"/>
+      <c r="T27" s="144"/>
+      <c r="U27" s="144"/>
+      <c r="V27" s="144"/>
+      <c r="W27" s="144"/>
+      <c r="X27" s="144"/>
+      <c r="Y27" s="144"/>
     </row>
     <row r="28" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="129"/>
-      <c r="B28" s="138" t="s">
+      <c r="A28" s="137"/>
+      <c r="B28" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="139"/>
-      <c r="D28" s="138" t="s">
+      <c r="C28" s="129"/>
+      <c r="D28" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="140"/>
-      <c r="F28" s="141" t="s">
+      <c r="E28" s="130"/>
+      <c r="F28" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="G28" s="153"/>
-      <c r="H28" s="143" t="s">
+      <c r="G28" s="132"/>
+      <c r="H28" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="I28" s="143"/>
-      <c r="J28" s="138" t="s">
+      <c r="I28" s="125"/>
+      <c r="J28" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="K28" s="139"/>
-      <c r="L28" s="138" t="s">
+      <c r="K28" s="129"/>
+      <c r="L28" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="M28" s="140"/>
-      <c r="N28" s="141" t="s">
+      <c r="M28" s="130"/>
+      <c r="N28" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="O28" s="153"/>
-      <c r="P28" s="146" t="s">
+      <c r="O28" s="132"/>
+      <c r="P28" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="Q28" s="159"/>
-      <c r="R28" s="160" t="s">
+      <c r="Q28" s="134"/>
+      <c r="R28" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="S28" s="160"/>
-      <c r="T28" s="160" t="s">
+      <c r="S28" s="135"/>
+      <c r="T28" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="U28" s="160"/>
-      <c r="V28" s="143" t="s">
+      <c r="U28" s="135"/>
+      <c r="V28" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="W28" s="143"/>
-      <c r="X28" s="143" t="s">
+      <c r="W28" s="125"/>
+      <c r="X28" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="Y28" s="143"/>
+      <c r="Y28" s="125"/>
     </row>
     <row r="29" spans="1:34" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="130"/>
+      <c r="A29" s="138"/>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
@@ -4969,31 +4969,31 @@
       <c r="Y50" s="52"/>
     </row>
     <row r="51" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A51" s="157" t="s">
+      <c r="A51" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="157"/>
-      <c r="C51" s="157"/>
-      <c r="D51" s="157"/>
-      <c r="E51" s="157"/>
-      <c r="F51" s="157"/>
-      <c r="G51" s="157"/>
-      <c r="H51" s="157"/>
-      <c r="I51" s="157"/>
-      <c r="J51" s="157"/>
-      <c r="K51" s="157"/>
-      <c r="L51" s="157"/>
-      <c r="M51" s="157"/>
-      <c r="N51" s="157"/>
-      <c r="O51" s="157"/>
-      <c r="P51" s="157"/>
-      <c r="Q51" s="157"/>
-      <c r="R51" s="158"/>
-      <c r="S51" s="158"/>
-      <c r="T51" s="158"/>
-      <c r="U51" s="158"/>
-      <c r="V51" s="158"/>
-      <c r="W51" s="158"/>
+      <c r="B51" s="126"/>
+      <c r="C51" s="126"/>
+      <c r="D51" s="126"/>
+      <c r="E51" s="126"/>
+      <c r="F51" s="126"/>
+      <c r="G51" s="126"/>
+      <c r="H51" s="126"/>
+      <c r="I51" s="126"/>
+      <c r="J51" s="126"/>
+      <c r="K51" s="126"/>
+      <c r="L51" s="126"/>
+      <c r="M51" s="126"/>
+      <c r="N51" s="126"/>
+      <c r="O51" s="126"/>
+      <c r="P51" s="126"/>
+      <c r="Q51" s="126"/>
+      <c r="R51" s="127"/>
+      <c r="S51" s="127"/>
+      <c r="T51" s="127"/>
+      <c r="U51" s="127"/>
+      <c r="V51" s="127"/>
+      <c r="W51" s="127"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="T53" s="57"/>
@@ -5019,6 +5019,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="J3:Q3"/>
+    <mergeCell ref="R3:Y3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="J4:K4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="V28:W28"/>
@@ -5035,25 +5054,6 @@
     <mergeCell ref="J27:Q27"/>
     <mergeCell ref="R27:Y27"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A2:W2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="J3:Q3"/>
-    <mergeCell ref="R3:Y3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -5080,12 +5080,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
       <c r="E1" s="59"/>
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
@@ -5218,12 +5218,12 @@
       <c r="D10" s="89"/>
     </row>
     <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="122" t="s">
+      <c r="A11" s="157" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
+      <c r="B11" s="157"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
       <c r="E11" s="67"/>
       <c r="G11" s="67"/>
     </row>
@@ -5318,12 +5318,12 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="122" t="s">
+      <c r="A18" s="157" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="157"/>
       <c r="E18" s="67"/>
       <c r="G18" s="67"/>
     </row>
@@ -5363,12 +5363,12 @@
       <c r="D21" s="89"/>
     </row>
     <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="122" t="s">
+      <c r="A22" s="157" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="122"/>
-      <c r="C22" s="122"/>
-      <c r="D22" s="122"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="71" t="s">
@@ -5419,12 +5419,12 @@
       <c r="L26" s="62"/>
     </row>
     <row r="27" spans="1:12" s="102" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="125" t="s">
+      <c r="A27" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="125"/>
-      <c r="C27" s="125"/>
-      <c r="D27" s="125"/>
+      <c r="B27" s="160"/>
+      <c r="C27" s="160"/>
+      <c r="D27" s="160"/>
       <c r="E27" s="60"/>
       <c r="G27" s="60"/>
       <c r="H27" s="62"/>
@@ -5474,12 +5474,12 @@
       <c r="G30" s="67"/>
     </row>
     <row r="31" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="122" t="s">
+      <c r="A31" s="157" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="122"/>
-      <c r="C31" s="122"/>
-      <c r="D31" s="122"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="157"/>
+      <c r="D31" s="157"/>
       <c r="E31" s="67"/>
       <c r="G31" s="67"/>
     </row>
@@ -5580,12 +5580,12 @@
       <c r="L36" s="62"/>
     </row>
     <row r="37" spans="1:12" s="102" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="122" t="s">
+      <c r="A37" s="157" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="122"/>
-      <c r="C37" s="122"/>
-      <c r="D37" s="122"/>
+      <c r="B37" s="157"/>
+      <c r="C37" s="157"/>
+      <c r="D37" s="157"/>
       <c r="E37" s="60"/>
       <c r="G37" s="60"/>
       <c r="H37" s="62"/>
@@ -5679,12 +5679,12 @@
       <c r="L41" s="62"/>
     </row>
     <row r="42" spans="1:12" s="88" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="123" t="s">
+      <c r="A42" s="158" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="123"/>
-      <c r="C42" s="123"/>
-      <c r="D42" s="123"/>
+      <c r="B42" s="158"/>
+      <c r="C42" s="158"/>
+      <c r="D42" s="158"/>
       <c r="E42" s="116"/>
       <c r="F42" s="116"/>
       <c r="G42" s="116"/>
@@ -5695,12 +5695,12 @@
       <c r="L42" s="117"/>
     </row>
     <row r="43" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="124" t="s">
+      <c r="A43" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="124"/>
-      <c r="C43" s="124"/>
-      <c r="D43" s="124"/>
+      <c r="B43" s="159"/>
+      <c r="C43" s="159"/>
+      <c r="D43" s="159"/>
       <c r="E43" s="119"/>
       <c r="F43" s="120"/>
       <c r="G43" s="120"/>

--- a/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
+++ b/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/CMMBML_Sobremesas_Modradas/BrechaPensiones21mayo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB60EA95-D2FC-4BB0-B434-386303B2B7E7}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D3F9F39-4119-4C87-8E56-7889521F201B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B4F7930C-2F0B-4481-8C8E-754286E3F8C0}"/>
   </bookViews>
@@ -1116,6 +1116,72 @@
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1125,48 +1191,18 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="5" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="4" fillId="6" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1183,42 +1219,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="18" fillId="2" borderId="26" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1584,147 +1584,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
-      <c r="U1" s="145"/>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
     </row>
     <row r="2" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="146" t="s">
+      <c r="A2" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="146"/>
-      <c r="Q2" s="146"/>
-      <c r="R2" s="145"/>
-      <c r="S2" s="145"/>
-      <c r="T2" s="145"/>
-      <c r="U2" s="145"/>
-      <c r="V2" s="145"/>
-      <c r="W2" s="145"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="128"/>
+      <c r="S2" s="128"/>
+      <c r="T2" s="128"/>
+      <c r="U2" s="128"/>
+      <c r="V2" s="128"/>
+      <c r="W2" s="128"/>
     </row>
     <row r="3" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="136" t="s">
+      <c r="A3" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="147" t="s">
+      <c r="B3" s="133" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="148"/>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="148"/>
-      <c r="H3" s="148"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="150" t="s">
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="136" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="151"/>
-      <c r="L3" s="151"/>
-      <c r="M3" s="151"/>
-      <c r="N3" s="151"/>
-      <c r="O3" s="151"/>
-      <c r="P3" s="151"/>
-      <c r="Q3" s="152"/>
-      <c r="R3" s="153" t="s">
+      <c r="K3" s="137"/>
+      <c r="L3" s="137"/>
+      <c r="M3" s="137"/>
+      <c r="N3" s="137"/>
+      <c r="O3" s="137"/>
+      <c r="P3" s="137"/>
+      <c r="Q3" s="138"/>
+      <c r="R3" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="S3" s="153"/>
-      <c r="T3" s="153"/>
-      <c r="U3" s="153"/>
-      <c r="V3" s="153"/>
-      <c r="W3" s="153"/>
-      <c r="X3" s="153"/>
-      <c r="Y3" s="153"/>
+      <c r="S3" s="139"/>
+      <c r="T3" s="139"/>
+      <c r="U3" s="139"/>
+      <c r="V3" s="139"/>
+      <c r="W3" s="139"/>
+      <c r="X3" s="139"/>
+      <c r="Y3" s="139"/>
     </row>
     <row r="4" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="137"/>
-      <c r="B4" s="128" t="s">
+      <c r="A4" s="131"/>
+      <c r="B4" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="129"/>
-      <c r="D4" s="128" t="s">
+      <c r="C4" s="140"/>
+      <c r="D4" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="130"/>
-      <c r="F4" s="131" t="s">
+      <c r="E4" s="123"/>
+      <c r="F4" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="154"/>
-      <c r="H4" s="125" t="s">
+      <c r="G4" s="141"/>
+      <c r="H4" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="125"/>
-      <c r="J4" s="128" t="s">
+      <c r="I4" s="127"/>
+      <c r="J4" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="129"/>
-      <c r="L4" s="128" t="s">
+      <c r="K4" s="140"/>
+      <c r="L4" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="130"/>
-      <c r="N4" s="131" t="s">
+      <c r="M4" s="123"/>
+      <c r="N4" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="132"/>
-      <c r="P4" s="133" t="s">
+      <c r="O4" s="125"/>
+      <c r="P4" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="122" t="s">
+      <c r="Q4" s="126"/>
+      <c r="R4" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="S4" s="123"/>
-      <c r="T4" s="122" t="s">
+      <c r="S4" s="145"/>
+      <c r="T4" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="U4" s="124"/>
-      <c r="V4" s="155" t="s">
+      <c r="U4" s="146"/>
+      <c r="V4" s="142" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="156"/>
-      <c r="X4" s="133" t="s">
+      <c r="W4" s="143"/>
+      <c r="X4" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" s="133"/>
+      <c r="Y4" s="126"/>
     </row>
     <row r="5" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="138"/>
+      <c r="A5" s="132"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1870,11 +1870,11 @@
         <v>2803108</v>
       </c>
       <c r="W6" s="12">
-        <v>1262.9194898769315</v>
+        <v>1262.9194898769299</v>
       </c>
       <c r="X6" s="10">
         <f>(U6-W6)/U6</f>
-        <v>0.29486348635547921</v>
+        <v>0.2948634863554801</v>
       </c>
       <c r="Y6" s="10">
         <f>V6/R6</f>
@@ -3329,93 +3329,93 @@
       <c r="AH26" s="38"/>
     </row>
     <row r="27" spans="1:34" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="136" t="s">
+      <c r="A27" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="139" t="s">
+      <c r="B27" s="151" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="140"/>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="140"/>
-      <c r="I27" s="141"/>
-      <c r="J27" s="142" t="s">
+      <c r="C27" s="152"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="152"/>
+      <c r="G27" s="152"/>
+      <c r="H27" s="152"/>
+      <c r="I27" s="153"/>
+      <c r="J27" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="K27" s="143"/>
-      <c r="L27" s="143"/>
-      <c r="M27" s="143"/>
-      <c r="N27" s="143"/>
-      <c r="O27" s="143"/>
-      <c r="P27" s="143"/>
-      <c r="Q27" s="143"/>
-      <c r="R27" s="144" t="s">
+      <c r="K27" s="155"/>
+      <c r="L27" s="155"/>
+      <c r="M27" s="155"/>
+      <c r="N27" s="155"/>
+      <c r="O27" s="155"/>
+      <c r="P27" s="155"/>
+      <c r="Q27" s="155"/>
+      <c r="R27" s="156" t="s">
         <v>39</v>
       </c>
-      <c r="S27" s="144"/>
-      <c r="T27" s="144"/>
-      <c r="U27" s="144"/>
-      <c r="V27" s="144"/>
-      <c r="W27" s="144"/>
-      <c r="X27" s="144"/>
-      <c r="Y27" s="144"/>
+      <c r="S27" s="156"/>
+      <c r="T27" s="156"/>
+      <c r="U27" s="156"/>
+      <c r="V27" s="156"/>
+      <c r="W27" s="156"/>
+      <c r="X27" s="156"/>
+      <c r="Y27" s="156"/>
     </row>
     <row r="28" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="137"/>
-      <c r="B28" s="128" t="s">
+      <c r="A28" s="131"/>
+      <c r="B28" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="129"/>
-      <c r="D28" s="128" t="s">
+      <c r="C28" s="140"/>
+      <c r="D28" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="130"/>
-      <c r="F28" s="131" t="s">
+      <c r="E28" s="123"/>
+      <c r="F28" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="G28" s="132"/>
-      <c r="H28" s="125" t="s">
+      <c r="G28" s="125"/>
+      <c r="H28" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="I28" s="125"/>
-      <c r="J28" s="128" t="s">
+      <c r="I28" s="127"/>
+      <c r="J28" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="K28" s="129"/>
-      <c r="L28" s="128" t="s">
+      <c r="K28" s="140"/>
+      <c r="L28" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="M28" s="130"/>
-      <c r="N28" s="131" t="s">
+      <c r="M28" s="123"/>
+      <c r="N28" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="O28" s="132"/>
-      <c r="P28" s="133" t="s">
+      <c r="O28" s="125"/>
+      <c r="P28" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="Q28" s="134"/>
-      <c r="R28" s="135" t="s">
+      <c r="Q28" s="149"/>
+      <c r="R28" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="S28" s="135"/>
-      <c r="T28" s="135" t="s">
+      <c r="S28" s="150"/>
+      <c r="T28" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="U28" s="135"/>
-      <c r="V28" s="125" t="s">
+      <c r="U28" s="150"/>
+      <c r="V28" s="127" t="s">
         <v>8</v>
       </c>
-      <c r="W28" s="125"/>
-      <c r="X28" s="125" t="s">
+      <c r="W28" s="127"/>
+      <c r="X28" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="Y28" s="125"/>
+      <c r="Y28" s="127"/>
     </row>
     <row r="29" spans="1:34" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="138"/>
+      <c r="A29" s="132"/>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
@@ -4049,8 +4049,8 @@
       <c r="G38" s="17">
         <v>1042.49569789675</v>
       </c>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
       <c r="J38" s="14">
         <v>4968</v>
       </c>
@@ -4114,8 +4114,8 @@
       <c r="G39" s="17">
         <v>1048.781930464042</v>
       </c>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
       <c r="J39" s="14">
         <v>7877</v>
       </c>
@@ -4179,8 +4179,8 @@
       <c r="G40" s="17">
         <v>1054.1608607344483</v>
       </c>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
       <c r="J40" s="14">
         <v>13951</v>
       </c>
@@ -4244,8 +4244,8 @@
       <c r="G41" s="17">
         <v>1021.444958967667</v>
       </c>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
       <c r="J41" s="14">
         <v>20676</v>
       </c>
@@ -4309,8 +4309,8 @@
       <c r="G42" s="17">
         <v>980.52934278938835</v>
       </c>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
       <c r="J42" s="14">
         <v>24860</v>
       </c>
@@ -4969,31 +4969,31 @@
       <c r="Y50" s="52"/>
     </row>
     <row r="51" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A51" s="126" t="s">
+      <c r="A51" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="126"/>
-      <c r="C51" s="126"/>
-      <c r="D51" s="126"/>
-      <c r="E51" s="126"/>
-      <c r="F51" s="126"/>
-      <c r="G51" s="126"/>
-      <c r="H51" s="126"/>
-      <c r="I51" s="126"/>
-      <c r="J51" s="126"/>
-      <c r="K51" s="126"/>
-      <c r="L51" s="126"/>
-      <c r="M51" s="126"/>
-      <c r="N51" s="126"/>
-      <c r="O51" s="126"/>
-      <c r="P51" s="126"/>
-      <c r="Q51" s="126"/>
-      <c r="R51" s="127"/>
-      <c r="S51" s="127"/>
-      <c r="T51" s="127"/>
-      <c r="U51" s="127"/>
-      <c r="V51" s="127"/>
-      <c r="W51" s="127"/>
+      <c r="B51" s="147"/>
+      <c r="C51" s="147"/>
+      <c r="D51" s="147"/>
+      <c r="E51" s="147"/>
+      <c r="F51" s="147"/>
+      <c r="G51" s="147"/>
+      <c r="H51" s="147"/>
+      <c r="I51" s="147"/>
+      <c r="J51" s="147"/>
+      <c r="K51" s="147"/>
+      <c r="L51" s="147"/>
+      <c r="M51" s="147"/>
+      <c r="N51" s="147"/>
+      <c r="O51" s="147"/>
+      <c r="P51" s="147"/>
+      <c r="Q51" s="147"/>
+      <c r="R51" s="148"/>
+      <c r="S51" s="148"/>
+      <c r="T51" s="148"/>
+      <c r="U51" s="148"/>
+      <c r="V51" s="148"/>
+      <c r="W51" s="148"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="T53" s="57"/>
@@ -5019,12 +5019,20 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="A51:W51"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="J27:Q27"/>
+    <mergeCell ref="R27:Y27"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A3:A5"/>
@@ -5040,20 +5048,12 @@
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="A51:W51"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="J27:Q27"/>
-    <mergeCell ref="R27:Y27"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>

--- a/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
+++ b/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/CMMBML_Sobremesas_Modradas/BrechaPensiones21mayo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D3F9F39-4119-4C87-8E56-7889521F201B}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{884064D1-0D2A-489A-BF19-1C743D70912A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B4F7930C-2F0B-4481-8C8E-754286E3F8C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B4F7930C-2F0B-4481-8C8E-754286E3F8C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Edades_Total sistema" sheetId="1" r:id="rId1"/>
@@ -5273,6 +5273,10 @@
         <v>63896</v>
       </c>
       <c r="E14" s="84"/>
+      <c r="F14" s="60">
+        <f>C14/C5</f>
+        <v>0.2992991104044555</v>
+      </c>
       <c r="G14" s="67"/>
     </row>
     <row r="15" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
+++ b/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/CMMBML_Sobremesas_Modradas/BrechaPensiones21mayo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{884064D1-0D2A-489A-BF19-1C743D70912A}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{275D41BE-D308-4F8C-9730-364A0CB98A03}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B4F7930C-2F0B-4481-8C8E-754286E3F8C0}"/>
   </bookViews>
@@ -5273,10 +5273,6 @@
         <v>63896</v>
       </c>
       <c r="E14" s="84"/>
-      <c r="F14" s="60">
-        <f>C14/C5</f>
-        <v>0.2992991104044555</v>
-      </c>
       <c r="G14" s="67"/>
     </row>
     <row r="15" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
+++ b/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/CMMBML_Sobremesas_Modradas/BrechaPensiones21mayo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{275D41BE-D308-4F8C-9730-364A0CB98A03}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D060B136-654C-4A71-8872-B6CB523FC495}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B4F7930C-2F0B-4481-8C8E-754286E3F8C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B4F7930C-2F0B-4481-8C8E-754286E3F8C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Edades_Total sistema" sheetId="1" r:id="rId1"/>
@@ -785,7 +785,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="18" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1116,111 +1116,6 @@
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="5" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="6" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="6" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="7" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="7" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="18" fillId="2" borderId="26" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1234,6 +1129,112 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="5" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="6" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="6" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="7" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="7" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -1583,148 +1584,148 @@
     <col min="24" max="16384" width="11.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="128" t="s">
+    <row r="1" spans="1:27" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128"/>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="128"/>
-      <c r="S1" s="128"/>
-      <c r="T1" s="128"/>
-      <c r="U1" s="128"/>
-      <c r="V1" s="128"/>
-      <c r="W1" s="128"/>
-    </row>
-    <row r="2" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="129" t="s">
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="146"/>
+      <c r="U1" s="146"/>
+      <c r="V1" s="146"/>
+      <c r="W1" s="146"/>
+    </row>
+    <row r="2" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="147" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="129"/>
-      <c r="R2" s="128"/>
-      <c r="S2" s="128"/>
-      <c r="T2" s="128"/>
-      <c r="U2" s="128"/>
-      <c r="V2" s="128"/>
-      <c r="W2" s="128"/>
-    </row>
-    <row r="3" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="130" t="s">
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="146"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="146"/>
+      <c r="U2" s="146"/>
+      <c r="V2" s="146"/>
+      <c r="W2" s="146"/>
+    </row>
+    <row r="3" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="133" t="s">
+      <c r="B3" s="148" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="135"/>
-      <c r="J3" s="136" t="s">
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="149"/>
+      <c r="G3" s="149"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="137"/>
-      <c r="L3" s="137"/>
-      <c r="M3" s="137"/>
-      <c r="N3" s="137"/>
-      <c r="O3" s="137"/>
-      <c r="P3" s="137"/>
-      <c r="Q3" s="138"/>
-      <c r="R3" s="139" t="s">
+      <c r="K3" s="152"/>
+      <c r="L3" s="152"/>
+      <c r="M3" s="152"/>
+      <c r="N3" s="152"/>
+      <c r="O3" s="152"/>
+      <c r="P3" s="152"/>
+      <c r="Q3" s="153"/>
+      <c r="R3" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="S3" s="139"/>
-      <c r="T3" s="139"/>
-      <c r="U3" s="139"/>
-      <c r="V3" s="139"/>
-      <c r="W3" s="139"/>
-      <c r="X3" s="139"/>
-      <c r="Y3" s="139"/>
-    </row>
-    <row r="4" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="131"/>
-      <c r="B4" s="122" t="s">
+      <c r="S3" s="154"/>
+      <c r="T3" s="154"/>
+      <c r="U3" s="154"/>
+      <c r="V3" s="154"/>
+      <c r="W3" s="154"/>
+      <c r="X3" s="154"/>
+      <c r="Y3" s="154"/>
+    </row>
+    <row r="4" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="138"/>
+      <c r="B4" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="140"/>
-      <c r="D4" s="122" t="s">
+      <c r="C4" s="130"/>
+      <c r="D4" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="123"/>
-      <c r="F4" s="124" t="s">
+      <c r="E4" s="131"/>
+      <c r="F4" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="141"/>
-      <c r="H4" s="127" t="s">
+      <c r="G4" s="155"/>
+      <c r="H4" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="127"/>
-      <c r="J4" s="122" t="s">
+      <c r="I4" s="126"/>
+      <c r="J4" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="140"/>
-      <c r="L4" s="122" t="s">
+      <c r="K4" s="130"/>
+      <c r="L4" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="123"/>
-      <c r="N4" s="124" t="s">
+      <c r="M4" s="131"/>
+      <c r="N4" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="125"/>
-      <c r="P4" s="126" t="s">
+      <c r="O4" s="133"/>
+      <c r="P4" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="144" t="s">
+      <c r="Q4" s="134"/>
+      <c r="R4" s="158" t="s">
         <v>6</v>
       </c>
-      <c r="S4" s="145"/>
-      <c r="T4" s="144" t="s">
+      <c r="S4" s="159"/>
+      <c r="T4" s="158" t="s">
         <v>7</v>
       </c>
-      <c r="U4" s="146"/>
-      <c r="V4" s="142" t="s">
+      <c r="U4" s="160"/>
+      <c r="V4" s="156" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="143"/>
-      <c r="X4" s="126" t="s">
+      <c r="W4" s="157"/>
+      <c r="X4" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" s="126"/>
-    </row>
-    <row r="5" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="132"/>
+      <c r="Y4" s="134"/>
+    </row>
+    <row r="5" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="139"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1798,7 +1799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
@@ -1880,8 +1881,12 @@
         <f>V6/R6</f>
         <v>0.41908395634099832</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="AA6" s="161">
+        <f>R6/B6</f>
+        <v>0.63845389779552619</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>15</v>
       </c>
@@ -1946,7 +1951,7 @@
       <c r="X7" s="22"/>
       <c r="Y7" s="22"/>
     </row>
-    <row r="8" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
         <v>17</v>
       </c>
@@ -2011,7 +2016,7 @@
       <c r="X8" s="22"/>
       <c r="Y8" s="22"/>
     </row>
-    <row r="9" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="23" t="s">
         <v>18</v>
       </c>
@@ -2076,7 +2081,7 @@
       <c r="X9" s="22"/>
       <c r="Y9" s="22"/>
     </row>
-    <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="23" t="s">
         <v>19</v>
       </c>
@@ -2141,7 +2146,7 @@
       <c r="X10" s="22"/>
       <c r="Y10" s="22"/>
     </row>
-    <row r="11" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="23" t="s">
         <v>20</v>
       </c>
@@ -2206,7 +2211,7 @@
       <c r="X11" s="22"/>
       <c r="Y11" s="22"/>
     </row>
-    <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
         <v>21</v>
       </c>
@@ -2271,7 +2276,7 @@
       <c r="X12" s="22"/>
       <c r="Y12" s="22"/>
     </row>
-    <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>22</v>
       </c>
@@ -2336,7 +2341,7 @@
       <c r="X13" s="22"/>
       <c r="Y13" s="22"/>
     </row>
-    <row r="14" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>23</v>
       </c>
@@ -2401,7 +2406,7 @@
       <c r="X14" s="22"/>
       <c r="Y14" s="22"/>
     </row>
-    <row r="15" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>24</v>
       </c>
@@ -2466,7 +2471,7 @@
       <c r="X15" s="22"/>
       <c r="Y15" s="22"/>
     </row>
-    <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>25</v>
       </c>
@@ -3329,93 +3334,93 @@
       <c r="AH26" s="38"/>
     </row>
     <row r="27" spans="1:34" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="130" t="s">
+      <c r="A27" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="151" t="s">
+      <c r="B27" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="152"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="152"/>
-      <c r="I27" s="153"/>
-      <c r="J27" s="154" t="s">
+      <c r="C27" s="141"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="141"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="141"/>
+      <c r="H27" s="141"/>
+      <c r="I27" s="142"/>
+      <c r="J27" s="143" t="s">
         <v>38</v>
       </c>
-      <c r="K27" s="155"/>
-      <c r="L27" s="155"/>
-      <c r="M27" s="155"/>
-      <c r="N27" s="155"/>
-      <c r="O27" s="155"/>
-      <c r="P27" s="155"/>
-      <c r="Q27" s="155"/>
-      <c r="R27" s="156" t="s">
+      <c r="K27" s="144"/>
+      <c r="L27" s="144"/>
+      <c r="M27" s="144"/>
+      <c r="N27" s="144"/>
+      <c r="O27" s="144"/>
+      <c r="P27" s="144"/>
+      <c r="Q27" s="144"/>
+      <c r="R27" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="S27" s="156"/>
-      <c r="T27" s="156"/>
-      <c r="U27" s="156"/>
-      <c r="V27" s="156"/>
-      <c r="W27" s="156"/>
-      <c r="X27" s="156"/>
-      <c r="Y27" s="156"/>
+      <c r="S27" s="145"/>
+      <c r="T27" s="145"/>
+      <c r="U27" s="145"/>
+      <c r="V27" s="145"/>
+      <c r="W27" s="145"/>
+      <c r="X27" s="145"/>
+      <c r="Y27" s="145"/>
     </row>
     <row r="28" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="131"/>
-      <c r="B28" s="122" t="s">
+      <c r="A28" s="138"/>
+      <c r="B28" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="140"/>
-      <c r="D28" s="122" t="s">
+      <c r="C28" s="130"/>
+      <c r="D28" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="123"/>
-      <c r="F28" s="124" t="s">
+      <c r="E28" s="131"/>
+      <c r="F28" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="G28" s="125"/>
-      <c r="H28" s="127" t="s">
+      <c r="G28" s="133"/>
+      <c r="H28" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="I28" s="127"/>
-      <c r="J28" s="122" t="s">
+      <c r="I28" s="126"/>
+      <c r="J28" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="K28" s="140"/>
-      <c r="L28" s="122" t="s">
+      <c r="K28" s="130"/>
+      <c r="L28" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="M28" s="123"/>
-      <c r="N28" s="124" t="s">
+      <c r="M28" s="131"/>
+      <c r="N28" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="O28" s="125"/>
-      <c r="P28" s="126" t="s">
+      <c r="O28" s="133"/>
+      <c r="P28" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="Q28" s="149"/>
-      <c r="R28" s="150" t="s">
+      <c r="Q28" s="135"/>
+      <c r="R28" s="136" t="s">
         <v>6</v>
       </c>
-      <c r="S28" s="150"/>
-      <c r="T28" s="150" t="s">
+      <c r="S28" s="136"/>
+      <c r="T28" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="U28" s="150"/>
-      <c r="V28" s="127" t="s">
+      <c r="U28" s="136"/>
+      <c r="V28" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="W28" s="127"/>
-      <c r="X28" s="127" t="s">
+      <c r="W28" s="126"/>
+      <c r="X28" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="Y28" s="127"/>
+      <c r="Y28" s="126"/>
     </row>
     <row r="29" spans="1:34" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="132"/>
+      <c r="A29" s="139"/>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
@@ -4969,31 +4974,31 @@
       <c r="Y50" s="52"/>
     </row>
     <row r="51" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A51" s="147" t="s">
+      <c r="A51" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="147"/>
-      <c r="C51" s="147"/>
-      <c r="D51" s="147"/>
-      <c r="E51" s="147"/>
-      <c r="F51" s="147"/>
-      <c r="G51" s="147"/>
-      <c r="H51" s="147"/>
-      <c r="I51" s="147"/>
-      <c r="J51" s="147"/>
-      <c r="K51" s="147"/>
-      <c r="L51" s="147"/>
-      <c r="M51" s="147"/>
-      <c r="N51" s="147"/>
-      <c r="O51" s="147"/>
-      <c r="P51" s="147"/>
-      <c r="Q51" s="147"/>
-      <c r="R51" s="148"/>
-      <c r="S51" s="148"/>
-      <c r="T51" s="148"/>
-      <c r="U51" s="148"/>
-      <c r="V51" s="148"/>
-      <c r="W51" s="148"/>
+      <c r="B51" s="127"/>
+      <c r="C51" s="127"/>
+      <c r="D51" s="127"/>
+      <c r="E51" s="127"/>
+      <c r="F51" s="127"/>
+      <c r="G51" s="127"/>
+      <c r="H51" s="127"/>
+      <c r="I51" s="127"/>
+      <c r="J51" s="127"/>
+      <c r="K51" s="127"/>
+      <c r="L51" s="127"/>
+      <c r="M51" s="127"/>
+      <c r="N51" s="127"/>
+      <c r="O51" s="127"/>
+      <c r="P51" s="127"/>
+      <c r="Q51" s="127"/>
+      <c r="R51" s="128"/>
+      <c r="S51" s="128"/>
+      <c r="T51" s="128"/>
+      <c r="U51" s="128"/>
+      <c r="V51" s="128"/>
+      <c r="W51" s="128"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="T53" s="57"/>
@@ -5019,20 +5024,11 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="A51:W51"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="J27:Q27"/>
-    <mergeCell ref="R27:Y27"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A3:A5"/>
@@ -5049,11 +5045,20 @@
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="A51:W51"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="J27:Q27"/>
+    <mergeCell ref="R27:Y27"/>
+    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -5080,12 +5085,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="125" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
       <c r="E1" s="59"/>
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
@@ -5218,12 +5223,12 @@
       <c r="D10" s="89"/>
     </row>
     <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="157" t="s">
+      <c r="A11" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="157"/>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
       <c r="E11" s="67"/>
       <c r="G11" s="67"/>
     </row>
@@ -5318,12 +5323,12 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="157" t="s">
+      <c r="A18" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="157"/>
-      <c r="C18" s="157"/>
-      <c r="D18" s="157"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
       <c r="E18" s="67"/>
       <c r="G18" s="67"/>
     </row>
@@ -5363,12 +5368,12 @@
       <c r="D21" s="89"/>
     </row>
     <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="157" t="s">
+      <c r="A22" s="122" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="157"/>
-      <c r="C22" s="157"/>
-      <c r="D22" s="157"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="122"/>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="71" t="s">
@@ -5419,12 +5424,12 @@
       <c r="L26" s="62"/>
     </row>
     <row r="27" spans="1:12" s="102" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="160" t="s">
+      <c r="A27" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="160"/>
-      <c r="C27" s="160"/>
-      <c r="D27" s="160"/>
+      <c r="B27" s="125"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="125"/>
       <c r="E27" s="60"/>
       <c r="G27" s="60"/>
       <c r="H27" s="62"/>
@@ -5474,12 +5479,12 @@
       <c r="G30" s="67"/>
     </row>
     <row r="31" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="157" t="s">
+      <c r="A31" s="122" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="157"/>
-      <c r="C31" s="157"/>
-      <c r="D31" s="157"/>
+      <c r="B31" s="122"/>
+      <c r="C31" s="122"/>
+      <c r="D31" s="122"/>
       <c r="E31" s="67"/>
       <c r="G31" s="67"/>
     </row>
@@ -5580,12 +5585,12 @@
       <c r="L36" s="62"/>
     </row>
     <row r="37" spans="1:12" s="102" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="157" t="s">
+      <c r="A37" s="122" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="157"/>
-      <c r="C37" s="157"/>
-      <c r="D37" s="157"/>
+      <c r="B37" s="122"/>
+      <c r="C37" s="122"/>
+      <c r="D37" s="122"/>
       <c r="E37" s="60"/>
       <c r="G37" s="60"/>
       <c r="H37" s="62"/>
@@ -5679,12 +5684,12 @@
       <c r="L41" s="62"/>
     </row>
     <row r="42" spans="1:12" s="88" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="158" t="s">
+      <c r="A42" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="158"/>
-      <c r="C42" s="158"/>
-      <c r="D42" s="158"/>
+      <c r="B42" s="123"/>
+      <c r="C42" s="123"/>
+      <c r="D42" s="123"/>
       <c r="E42" s="116"/>
       <c r="F42" s="116"/>
       <c r="G42" s="116"/>
@@ -5695,12 +5700,12 @@
       <c r="L42" s="117"/>
     </row>
     <row r="43" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="159" t="s">
+      <c r="A43" s="124" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="159"/>
-      <c r="C43" s="159"/>
-      <c r="D43" s="159"/>
+      <c r="B43" s="124"/>
+      <c r="C43" s="124"/>
+      <c r="D43" s="124"/>
       <c r="E43" s="119"/>
       <c r="F43" s="120"/>
       <c r="G43" s="120"/>

--- a/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
+++ b/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/CMMBML_Sobremesas_Modradas/BrechaPensiones21mayo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D060B136-654C-4A71-8872-B6CB523FC495}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D134E5EE-5F02-422A-87CD-04F36A765F5C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B4F7930C-2F0B-4481-8C8E-754286E3F8C0}"/>
   </bookViews>
@@ -1881,10 +1881,7 @@
         <f>V6/R6</f>
         <v>0.41908395634099832</v>
       </c>
-      <c r="AA6" s="161">
-        <f>R6/B6</f>
-        <v>0.63845389779552619</v>
-      </c>
+      <c r="AA6" s="161"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">

--- a/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
+++ b/BrechaPensiones21mayo26/ResumenAbril2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd291838b10efa6/Documentos/GitHub/CMMBML_Sobremesas_Modradas/BrechaPensiones21mayo26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D134E5EE-5F02-422A-87CD-04F36A765F5C}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{61527733-7704-45B9-84E3-00E8323A9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3C36BFE-DA03-44A8-BA35-1DDA3C375CEF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B4F7930C-2F0B-4481-8C8E-754286E3F8C0}"/>
   </bookViews>
@@ -272,13 +272,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -1116,6 +1117,111 @@
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="5" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="6" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="6" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="7" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="7" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="18" fillId="2" borderId="26" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1129,112 +1235,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="5" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="6" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="6" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="7" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="7" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -1263,10 +1264,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1581,151 +1578,153 @@
     <col min="21" max="21" width="10.5703125" style="1" customWidth="1"/>
     <col min="22" max="22" width="14" style="1" customWidth="1"/>
     <col min="23" max="23" width="10.5703125" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="11.85546875" style="1"/>
+    <col min="24" max="26" width="11.85546875" style="1"/>
+    <col min="27" max="27" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="11.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="146"/>
-      <c r="S1" s="146"/>
-      <c r="T1" s="146"/>
-      <c r="U1" s="146"/>
-      <c r="V1" s="146"/>
-      <c r="W1" s="146"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
     </row>
     <row r="2" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="147" t="s">
+      <c r="A2" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
-      <c r="R2" s="146"/>
-      <c r="S2" s="146"/>
-      <c r="T2" s="146"/>
-      <c r="U2" s="146"/>
-      <c r="V2" s="146"/>
-      <c r="W2" s="146"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="128"/>
+      <c r="S2" s="128"/>
+      <c r="T2" s="128"/>
+      <c r="U2" s="128"/>
+      <c r="V2" s="128"/>
+      <c r="W2" s="128"/>
     </row>
     <row r="3" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="148" t="s">
+      <c r="B3" s="133" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="149"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="149"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="151" t="s">
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="136" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="152"/>
-      <c r="L3" s="152"/>
-      <c r="M3" s="152"/>
-      <c r="N3" s="152"/>
-      <c r="O3" s="152"/>
-      <c r="P3" s="152"/>
-      <c r="Q3" s="153"/>
-      <c r="R3" s="154" t="s">
+      <c r="K3" s="137"/>
+      <c r="L3" s="137"/>
+      <c r="M3" s="137"/>
+      <c r="N3" s="137"/>
+      <c r="O3" s="137"/>
+      <c r="P3" s="137"/>
+      <c r="Q3" s="138"/>
+      <c r="R3" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="S3" s="154"/>
-      <c r="T3" s="154"/>
-      <c r="U3" s="154"/>
-      <c r="V3" s="154"/>
-      <c r="W3" s="154"/>
-      <c r="X3" s="154"/>
-      <c r="Y3" s="154"/>
+      <c r="S3" s="139"/>
+      <c r="T3" s="139"/>
+      <c r="U3" s="139"/>
+      <c r="V3" s="139"/>
+      <c r="W3" s="139"/>
+      <c r="X3" s="139"/>
+      <c r="Y3" s="139"/>
     </row>
     <row r="4" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="138"/>
-      <c r="B4" s="129" t="s">
+      <c r="A4" s="131"/>
+      <c r="B4" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="129" t="s">
+      <c r="C4" s="140"/>
+      <c r="D4" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="131"/>
-      <c r="F4" s="132" t="s">
+      <c r="E4" s="126"/>
+      <c r="F4" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="155"/>
-      <c r="H4" s="126" t="s">
+      <c r="G4" s="141"/>
+      <c r="H4" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="126"/>
-      <c r="J4" s="129" t="s">
+      <c r="I4" s="127"/>
+      <c r="J4" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="130"/>
-      <c r="L4" s="129" t="s">
+      <c r="K4" s="140"/>
+      <c r="L4" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="131"/>
-      <c r="N4" s="132" t="s">
+      <c r="M4" s="126"/>
+      <c r="N4" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="133"/>
-      <c r="P4" s="134" t="s">
+      <c r="O4" s="123"/>
+      <c r="P4" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="134"/>
-      <c r="R4" s="158" t="s">
+      <c r="Q4" s="124"/>
+      <c r="R4" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="S4" s="159"/>
-      <c r="T4" s="158" t="s">
+      <c r="S4" s="145"/>
+      <c r="T4" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="U4" s="160"/>
-      <c r="V4" s="156" t="s">
+      <c r="U4" s="146"/>
+      <c r="V4" s="142" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="157"/>
-      <c r="X4" s="134" t="s">
+      <c r="W4" s="143"/>
+      <c r="X4" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" s="134"/>
+      <c r="Y4" s="124"/>
     </row>
     <row r="5" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="139"/>
+      <c r="A5" s="132"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1881,7 +1880,10 @@
         <f>V6/R6</f>
         <v>0.41908395634099832</v>
       </c>
-      <c r="AA6" s="161"/>
+      <c r="AA6" s="161">
+        <f>B6*C6</f>
+        <v>14336235196.500195</v>
+      </c>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
@@ -3331,93 +3333,93 @@
       <c r="AH26" s="38"/>
     </row>
     <row r="27" spans="1:34" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="137" t="s">
+      <c r="A27" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="140" t="s">
+      <c r="B27" s="151" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="141"/>
-      <c r="D27" s="141"/>
-      <c r="E27" s="141"/>
-      <c r="F27" s="141"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="141"/>
-      <c r="I27" s="142"/>
-      <c r="J27" s="143" t="s">
+      <c r="C27" s="152"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="152"/>
+      <c r="G27" s="152"/>
+      <c r="H27" s="152"/>
+      <c r="I27" s="153"/>
+      <c r="J27" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="K27" s="144"/>
-      <c r="L27" s="144"/>
-      <c r="M27" s="144"/>
-      <c r="N27" s="144"/>
-      <c r="O27" s="144"/>
-      <c r="P27" s="144"/>
-      <c r="Q27" s="144"/>
-      <c r="R27" s="145" t="s">
+      <c r="K27" s="155"/>
+      <c r="L27" s="155"/>
+      <c r="M27" s="155"/>
+      <c r="N27" s="155"/>
+      <c r="O27" s="155"/>
+      <c r="P27" s="155"/>
+      <c r="Q27" s="155"/>
+      <c r="R27" s="156" t="s">
         <v>39</v>
       </c>
-      <c r="S27" s="145"/>
-      <c r="T27" s="145"/>
-      <c r="U27" s="145"/>
-      <c r="V27" s="145"/>
-      <c r="W27" s="145"/>
-      <c r="X27" s="145"/>
-      <c r="Y27" s="145"/>
+      <c r="S27" s="156"/>
+      <c r="T27" s="156"/>
+      <c r="U27" s="156"/>
+      <c r="V27" s="156"/>
+      <c r="W27" s="156"/>
+      <c r="X27" s="156"/>
+      <c r="Y27" s="156"/>
     </row>
     <row r="28" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="138"/>
-      <c r="B28" s="129" t="s">
+      <c r="A28" s="131"/>
+      <c r="B28" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="130"/>
-      <c r="D28" s="129" t="s">
+      <c r="C28" s="140"/>
+      <c r="D28" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="131"/>
-      <c r="F28" s="132" t="s">
+      <c r="E28" s="126"/>
+      <c r="F28" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="G28" s="133"/>
-      <c r="H28" s="126" t="s">
+      <c r="G28" s="123"/>
+      <c r="H28" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="I28" s="126"/>
-      <c r="J28" s="129" t="s">
+      <c r="I28" s="127"/>
+      <c r="J28" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="K28" s="130"/>
-      <c r="L28" s="129" t="s">
+      <c r="K28" s="140"/>
+      <c r="L28" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="M28" s="131"/>
-      <c r="N28" s="132" t="s">
+      <c r="M28" s="126"/>
+      <c r="N28" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="O28" s="133"/>
-      <c r="P28" s="134" t="s">
+      <c r="O28" s="123"/>
+      <c r="P28" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="Q28" s="135"/>
-      <c r="R28" s="136" t="s">
+      <c r="Q28" s="149"/>
+      <c r="R28" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="S28" s="136"/>
-      <c r="T28" s="136" t="s">
+      <c r="S28" s="150"/>
+      <c r="T28" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="U28" s="136"/>
-      <c r="V28" s="126" t="s">
+      <c r="U28" s="150"/>
+      <c r="V28" s="127" t="s">
         <v>8</v>
       </c>
-      <c r="W28" s="126"/>
-      <c r="X28" s="126" t="s">
+      <c r="W28" s="127"/>
+      <c r="X28" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="Y28" s="126"/>
+      <c r="Y28" s="127"/>
     </row>
     <row r="29" spans="1:34" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="139"/>
+      <c r="A29" s="132"/>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
@@ -4971,31 +4973,31 @@
       <c r="Y50" s="52"/>
     </row>
     <row r="51" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A51" s="127" t="s">
+      <c r="A51" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="127"/>
-      <c r="C51" s="127"/>
-      <c r="D51" s="127"/>
-      <c r="E51" s="127"/>
-      <c r="F51" s="127"/>
-      <c r="G51" s="127"/>
-      <c r="H51" s="127"/>
-      <c r="I51" s="127"/>
-      <c r="J51" s="127"/>
-      <c r="K51" s="127"/>
-      <c r="L51" s="127"/>
-      <c r="M51" s="127"/>
-      <c r="N51" s="127"/>
-      <c r="O51" s="127"/>
-      <c r="P51" s="127"/>
-      <c r="Q51" s="127"/>
-      <c r="R51" s="128"/>
-      <c r="S51" s="128"/>
-      <c r="T51" s="128"/>
-      <c r="U51" s="128"/>
-      <c r="V51" s="128"/>
-      <c r="W51" s="128"/>
+      <c r="B51" s="147"/>
+      <c r="C51" s="147"/>
+      <c r="D51" s="147"/>
+      <c r="E51" s="147"/>
+      <c r="F51" s="147"/>
+      <c r="G51" s="147"/>
+      <c r="H51" s="147"/>
+      <c r="I51" s="147"/>
+      <c r="J51" s="147"/>
+      <c r="K51" s="147"/>
+      <c r="L51" s="147"/>
+      <c r="M51" s="147"/>
+      <c r="N51" s="147"/>
+      <c r="O51" s="147"/>
+      <c r="P51" s="147"/>
+      <c r="Q51" s="147"/>
+      <c r="R51" s="148"/>
+      <c r="S51" s="148"/>
+      <c r="T51" s="148"/>
+      <c r="U51" s="148"/>
+      <c r="V51" s="148"/>
+      <c r="W51" s="148"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="T53" s="57"/>
@@ -5021,11 +5023,20 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="A51:W51"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="J27:Q27"/>
+    <mergeCell ref="R27:Y27"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A3:A5"/>
@@ -5042,20 +5053,11 @@
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="L4:M4"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="A51:W51"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="J27:Q27"/>
-    <mergeCell ref="R27:Y27"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -5082,12 +5084,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
       <c r="E1" s="59"/>
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
@@ -5220,12 +5222,12 @@
       <c r="D10" s="89"/>
     </row>
     <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="122" t="s">
+      <c r="A11" s="157" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
+      <c r="B11" s="157"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
       <c r="E11" s="67"/>
       <c r="G11" s="67"/>
     </row>
@@ -5320,12 +5322,12 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="122" t="s">
+      <c r="A18" s="157" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="157"/>
       <c r="E18" s="67"/>
       <c r="G18" s="67"/>
     </row>
@@ -5365,12 +5367,12 @@
       <c r="D21" s="89"/>
     </row>
     <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="122" t="s">
+      <c r="A22" s="157" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="122"/>
-      <c r="C22" s="122"/>
-      <c r="D22" s="122"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="71" t="s">
@@ -5421,12 +5423,12 @@
       <c r="L26" s="62"/>
     </row>
     <row r="27" spans="1:12" s="102" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="125" t="s">
+      <c r="A27" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="125"/>
-      <c r="C27" s="125"/>
-      <c r="D27" s="125"/>
+      <c r="B27" s="160"/>
+      <c r="C27" s="160"/>
+      <c r="D27" s="160"/>
       <c r="E27" s="60"/>
       <c r="G27" s="60"/>
       <c r="H27" s="62"/>
@@ -5476,12 +5478,12 @@
       <c r="G30" s="67"/>
     </row>
     <row r="31" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="122" t="s">
+      <c r="A31" s="157" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="122"/>
-      <c r="C31" s="122"/>
-      <c r="D31" s="122"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="157"/>
+      <c r="D31" s="157"/>
       <c r="E31" s="67"/>
       <c r="G31" s="67"/>
     </row>
@@ -5582,12 +5584,12 @@
       <c r="L36" s="62"/>
     </row>
     <row r="37" spans="1:12" s="102" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="122" t="s">
+      <c r="A37" s="157" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="122"/>
-      <c r="C37" s="122"/>
-      <c r="D37" s="122"/>
+      <c r="B37" s="157"/>
+      <c r="C37" s="157"/>
+      <c r="D37" s="157"/>
       <c r="E37" s="60"/>
       <c r="G37" s="60"/>
       <c r="H37" s="62"/>
@@ -5681,12 +5683,12 @@
       <c r="L41" s="62"/>
     </row>
     <row r="42" spans="1:12" s="88" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="123" t="s">
+      <c r="A42" s="158" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="123"/>
-      <c r="C42" s="123"/>
-      <c r="D42" s="123"/>
+      <c r="B42" s="158"/>
+      <c r="C42" s="158"/>
+      <c r="D42" s="158"/>
       <c r="E42" s="116"/>
       <c r="F42" s="116"/>
       <c r="G42" s="116"/>
@@ -5697,12 +5699,12 @@
       <c r="L42" s="117"/>
     </row>
     <row r="43" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="124" t="s">
+      <c r="A43" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="124"/>
-      <c r="C43" s="124"/>
-      <c r="D43" s="124"/>
+      <c r="B43" s="159"/>
+      <c r="C43" s="159"/>
+      <c r="D43" s="159"/>
       <c r="E43" s="119"/>
       <c r="F43" s="120"/>
       <c r="G43" s="120"/>
